--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="85">
   <si>
     <t>Mat</t>
   </si>
@@ -82,51 +82,60 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ADELL</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>NICIO</t>
   </si>
   <si>
-    <t>XOCUA</t>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>BERISTAIN</t>
   </si>
   <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -142,85 +151,112 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>CASTRO</t>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>GALEOTE</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>IRVING URIEL</t>
   </si>
   <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
     <t>JOSE JULIAN</t>
   </si>
   <si>
-    <t>MARCOS URIEL</t>
+    <t>ANGEL AMILCAR</t>
   </si>
   <si>
     <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
   </si>
   <si>
     <t>GERMAN ISAI</t>
@@ -674,7 +710,7 @@
         <v>82.86</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -831,16 +867,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>74.19</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -854,16 +893,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>74.29000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -877,16 +919,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -900,16 +945,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>35</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>94.59</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -923,16 +971,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H6">
+        <v>6.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -946,16 +997,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>22</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>68.75</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1020,7 +1074,7 @@
         <v>74.19</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1037,16 +1091,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>82.86</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1063,13 +1117,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
         <v>6.7</v>
@@ -1098,7 +1152,7 @@
         <v>94.59</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1124,7 +1178,7 @@
         <v>83.33</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1150,7 +1204,7 @@
         <v>68.75</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1192,16 +1246,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920013</v>
+        <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1215,16 +1269,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920016</v>
+        <v>20330051920013</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1238,16 +1292,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920025</v>
+        <v>20330051920016</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1261,16 +1315,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920035</v>
+        <v>20330051920021</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1284,16 +1338,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920374</v>
+        <v>20330051920237</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1307,16 +1361,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920237</v>
+        <v>20330051920240</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1330,16 +1384,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920251</v>
+        <v>20330051920241</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1353,22 +1407,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920178</v>
+        <v>20330051920244</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1376,22 +1430,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920286</v>
+        <v>20330051920251</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1399,22 +1453,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920297</v>
+        <v>20330051920178</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1422,16 +1476,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920299</v>
+        <v>20330051920286</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1445,16 +1499,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920301</v>
+        <v>20330051920297</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1468,16 +1522,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920308</v>
+        <v>20330051920299</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1491,16 +1545,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920311</v>
+        <v>20330051920301</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1514,68 +1568,68 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920034</v>
+        <v>20330051920308</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920228</v>
+        <v>20330051920311</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920243</v>
+        <v>20330051920363</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1583,22 +1637,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920365</v>
+        <v>20330051920025</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1606,22 +1660,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920284</v>
+        <v>20330051920034</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1629,24 +1683,139 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
+        <v>20330051920374</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920228</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920243</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920365</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920284</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
         <v>20330051920394</v>
       </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
         <v>14</v>
       </c>
-      <c r="G21">
+      <c r="G26">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="93">
   <si>
     <t>Mat</t>
   </si>
@@ -112,45 +112,51 @@
     <t>QUIRIZ</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>ALFONSO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -169,36 +175,45 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>PRADO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>MONTERROSAS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>CRISTOPHER ALAIN</t>
   </si>
   <si>
@@ -229,49 +244,58 @@
     <t>MONICA</t>
   </si>
   <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
     <t>AMERICA MICHELLE</t>
   </si>
   <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
     <t>ARIADNA</t>
   </si>
   <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
+    <t>JOSE ISAIAS</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>LISBETH ESMERALDA</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
     <t>MARIA MAGDALENA</t>
   </si>
   <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
     <t>MARISOL</t>
   </si>
   <si>
     <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>LISBETH ESMERALDA</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1252,10 +1276,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1275,10 +1299,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1298,10 +1322,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1321,10 +1345,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1347,7 +1371,7 @@
         <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1367,10 +1391,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1390,10 +1414,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1413,10 +1437,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1436,10 +1460,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1459,10 +1483,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1476,22 +1500,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920286</v>
+        <v>20330051920101</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1499,16 +1523,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920297</v>
+        <v>20330051920286</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1522,16 +1546,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920299</v>
+        <v>20330051920296</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1545,16 +1569,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920301</v>
+        <v>20330051920297</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1568,16 +1592,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920308</v>
+        <v>20330051920301</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1591,16 +1615,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920311</v>
+        <v>20330051920310</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1617,13 +1641,13 @@
         <v>20330051920363</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1640,13 +1664,13 @@
         <v>20330051920025</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1663,13 +1687,13 @@
         <v>20330051920034</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1686,13 +1710,13 @@
         <v>20330051920374</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1709,13 +1733,13 @@
         <v>20330051920228</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1735,10 +1759,10 @@
         <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1758,10 +1782,10 @@
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1781,10 +1805,10 @@
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1804,10 +1828,10 @@
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1816,6 +1840,75 @@
         <v>14</v>
       </c>
       <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920299</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920308</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920311</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -127,6 +127,9 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -154,9 +157,6 @@
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -262,6 +262,9 @@
     <t>ARANTZA</t>
   </si>
   <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
     <t>ANDRES NOEL</t>
   </si>
   <si>
@@ -293,9 +296,6 @@
   </si>
   <si>
     <t>MARISOL</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1368,7 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>69</v>
@@ -1391,7 +1391,7 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
         <v>70</v>
@@ -1483,7 +1483,7 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>74</v>
@@ -1638,13 +1638,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920363</v>
+        <v>20330051920311</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
         <v>81</v>
@@ -1653,21 +1653,21 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920025</v>
+        <v>20330051920363</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
         <v>82</v>
@@ -1684,13 +1684,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920034</v>
+        <v>20330051920025</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
         <v>83</v>
@@ -1707,13 +1707,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920374</v>
+        <v>20330051920034</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
@@ -1722,7 +1722,7 @@
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1730,13 +1730,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920228</v>
+        <v>20330051920374</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
         <v>85</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920243</v>
+        <v>20330051920228</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
         <v>86</v>
@@ -1776,13 +1776,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920365</v>
+        <v>20330051920243</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
         <v>87</v>
@@ -1791,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1799,13 +1799,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920284</v>
+        <v>20330051920365</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
         <v>88</v>
@@ -1814,7 +1814,7 @@
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1822,13 +1822,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920394</v>
+        <v>20330051920284</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
         <v>89</v>
@@ -1845,13 +1845,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920299</v>
+        <v>20330051920394</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
         <v>90</v>
@@ -1868,13 +1868,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920308</v>
+        <v>20330051920299</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
         <v>91</v>
@@ -1891,13 +1891,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920311</v>
+        <v>20330051920308</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
         <v>92</v>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="90">
   <si>
     <t>Mat</t>
   </si>
@@ -100,9 +100,6 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
@@ -166,9 +163,6 @@
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
     <t>LORENZO</t>
   </si>
   <si>
@@ -230,9 +224,6 @@
   </si>
   <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
   </si>
   <si>
     <t>VICTOR GAMALIEL</t>
@@ -1238,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1276,10 +1267,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1299,10 +1290,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1322,10 +1313,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1345,10 +1336,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1368,10 +1359,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1391,10 +1382,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1408,16 +1399,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920241</v>
+        <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1431,16 +1422,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1454,22 +1445,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920251</v>
+        <v>20330051920178</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1477,22 +1468,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920178</v>
+        <v>20330051920101</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1500,22 +1491,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920101</v>
+        <v>20330051920286</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1523,16 +1514,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920286</v>
+        <v>20330051920296</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1546,16 +1537,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920296</v>
+        <v>20330051920297</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1569,16 +1560,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920297</v>
+        <v>20330051920301</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1592,16 +1583,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920301</v>
+        <v>20330051920310</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1615,16 +1606,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920310</v>
+        <v>20330051920311</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1638,39 +1629,39 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920311</v>
+        <v>20330051920363</v>
       </c>
       <c r="B18" t="s">
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920363</v>
+        <v>20330051920025</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1684,16 +1675,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920025</v>
+        <v>20330051920034</v>
       </c>
       <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1707,22 +1698,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920034</v>
+        <v>20330051920374</v>
       </c>
       <c r="B21" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1730,16 +1721,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920374</v>
+        <v>20330051920228</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1753,16 +1744,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920228</v>
+        <v>20330051920243</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1776,22 +1767,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920243</v>
+        <v>20330051920365</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1799,22 +1790,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920365</v>
+        <v>20330051920284</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1822,16 +1813,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920284</v>
+        <v>20330051920394</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1845,16 +1836,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920394</v>
+        <v>20330051920299</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1868,16 +1859,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920299</v>
+        <v>20330051920308</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1886,29 +1877,6 @@
         <v>14</v>
       </c>
       <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920308</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="93">
   <si>
     <t>Mat</t>
   </si>
@@ -97,48 +97,51 @@
     <t>MARIANO</t>
   </si>
   <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
     <t>OLTEHUA</t>
   </si>
   <si>
@@ -169,39 +172,42 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ROSETE</t>
   </si>
   <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>MONTERROSAS</t>
   </si>
   <si>
@@ -223,64 +229,67 @@
     <t>JACQUELINE</t>
   </si>
   <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>VANNIA GISELLE</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>ANDRES NOEL</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>ANGEL AMILCAR</t>
+  </si>
+  <si>
+    <t>JOSE ISAIAS</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
+    <t>LISBETH ESMERALDA</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
   </si>
   <si>
     <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>LISBETH ESMERALDA</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
   </si>
   <si>
     <t>MARIA MAGDALENA</t>
@@ -1229,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1267,10 +1276,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1290,10 +1299,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1313,10 +1322,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1336,10 +1345,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1359,10 +1368,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1376,16 +1385,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920240</v>
+        <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1399,16 +1408,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1422,22 +1431,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920251</v>
+        <v>20330051920173</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1451,10 +1460,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1474,10 +1483,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1497,10 +1506,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1514,16 +1523,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920296</v>
+        <v>20330051920297</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1537,16 +1546,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920297</v>
+        <v>20330051920301</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1560,16 +1569,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920301</v>
+        <v>20330051920310</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1583,16 +1592,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920310</v>
+        <v>20330051920311</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1606,39 +1615,39 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920311</v>
+        <v>20330051920363</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920363</v>
+        <v>20330051920025</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1652,16 +1661,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920025</v>
+        <v>20330051920034</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1675,22 +1684,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920034</v>
+        <v>20330051920374</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1698,16 +1707,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920374</v>
+        <v>20330051920228</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1721,16 +1730,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920228</v>
+        <v>20330051920240</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1747,13 +1756,13 @@
         <v>20330051920243</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -1770,13 +1779,13 @@
         <v>20330051920365</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1793,13 +1802,13 @@
         <v>20330051920284</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1816,13 +1825,13 @@
         <v>20330051920394</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1836,16 +1845,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920299</v>
+        <v>20330051920296</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1859,16 +1868,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920308</v>
+        <v>20330051920299</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1877,6 +1886,29 @@
         <v>14</v>
       </c>
       <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920308</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
   <si>
     <t>Mat</t>
   </si>
@@ -103,90 +103,57 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>ALFONSO</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
   </si>
   <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
+    <t>TEXOCO</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
     <t>LORENZO</t>
   </si>
   <si>
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>ROSETE</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>AMADOR</t>
   </si>
   <si>
@@ -205,15 +172,6 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>CRISTOPHER ALAIN</t>
   </si>
   <si>
@@ -235,30 +193,9 @@
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
-    <t>VANNIA GISELLE</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
     <t>SERGIO MARIANO</t>
   </si>
   <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
     <t>ANDRES NOEL</t>
   </si>
   <si>
@@ -281,21 +218,6 @@
   </si>
   <si>
     <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
   </si>
 </sst>
 </file>
@@ -774,19 +696,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -826,19 +748,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -969,19 +891,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1021,19 +943,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1164,16 +1086,16 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>7.5</v>
@@ -1216,19 +1138,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1276,10 +1198,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1299,10 +1221,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1322,10 +1244,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1345,10 +1267,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1368,10 +1290,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1391,10 +1313,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1414,10 +1336,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1431,22 +1353,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920173</v>
+        <v>20330051920101</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1454,7 +1376,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920178</v>
+        <v>20330051920363</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -1463,452 +1385,176 @@
         <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920101</v>
+        <v>20330051920025</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920286</v>
+        <v>20330051920034</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920297</v>
+        <v>20330051920374</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920301</v>
+        <v>20330051920228</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920310</v>
+        <v>20330051920240</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920311</v>
+        <v>20330051920243</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920363</v>
+        <v>20330051920365</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920025</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920034</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920374</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920228</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920240</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920243</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920365</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920284</v>
-      </c>
-      <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920394</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920296</v>
-      </c>
-      <c r="B27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" t="s">
-        <v>90</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920299</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920308</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ADELL</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -103,43 +100,19 @@
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>TEXOCO</t>
+    <t>ACEVEDO</t>
   </si>
   <si>
     <t>ANTONIO</t>
@@ -154,34 +127,13 @@
     <t>ROSETE</t>
   </si>
   <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ALAIN</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>IRVING URIEL</t>
   </si>
   <si>
-    <t>OCTAVIO</t>
+    <t>GENARO RAFAEL</t>
   </si>
   <si>
     <t>JACQUELINE</t>
@@ -193,31 +145,10 @@
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
     <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>ANDRES NOEL</t>
-  </si>
-  <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ANGEL AMILCAR</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>LISBETH ESMERALDA</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
   </si>
 </sst>
 </file>
@@ -1011,16 +942,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>74.19</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1037,16 +968,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>74.29000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1063,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>95.23999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="H4">
         <v>6.7</v>
@@ -1098,7 +1029,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1115,16 +1046,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1150,7 +1081,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1192,16 +1123,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920002</v>
+        <v>20330051920013</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1215,16 +1146,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920013</v>
+        <v>20330051920016</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1238,22 +1169,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920016</v>
+        <v>20330051920236</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1261,22 +1192,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920021</v>
+        <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1284,16 +1215,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920237</v>
+        <v>20330051920244</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1307,16 +1238,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1330,22 +1261,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920251</v>
+        <v>20330051920354</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1359,10 +1290,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1372,190 +1303,6 @@
       </c>
       <c r="G9">
         <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920363</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920025</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920034</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920374</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920228</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920240</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920243</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920365</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -103,9 +103,6 @@
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
@@ -124,9 +121,6 @@
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
@@ -146,9 +140,6 @@
   </si>
   <si>
     <t>JAHEL</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1129,10 +1120,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1152,10 +1143,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1175,10 +1166,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1198,10 +1189,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1221,10 +1212,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1244,10 +1235,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1267,10 +1258,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1279,29 +1270,6 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920101</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -85,61 +85,70 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>VICTOR GAMALIEL</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
     <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>VICTOR GAMALIEL</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
   </si>
 </sst>
 </file>
@@ -1082,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1120,10 +1129,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1137,16 +1146,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920016</v>
+        <v>20330051920035</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1166,10 +1175,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1189,10 +1198,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1212,10 +1221,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1235,10 +1244,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1258,10 +1267,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1271,6 +1280,29 @@
       </c>
       <c r="G8">
         <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920016</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20221.xlsx
@@ -88,67 +88,67 @@
     <t>XOCUA</t>
   </si>
   <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>LORENZO</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>MARCOS URIEL</t>
   </si>
   <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
     <t>GENARO RAFAEL</t>
   </si>
   <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
     <t>VICTOR GAMALIEL</t>
   </si>
   <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
     <t>JAHEL</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920236</v>
+        <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920237</v>
+        <v>20330051920251</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920244</v>
+        <v>20330051920016</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -1230,15 +1230,15 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920251</v>
+        <v>20330051920236</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1256,12 +1256,12 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920354</v>
+        <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1276,21 +1276,21 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920016</v>
+        <v>20330051920354</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>43</v>
@@ -1299,7 +1299,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
